--- a/consultant_safe_v4/EBX_Q_템플릿_EM_추출·광물가공_중소_consultant_safe_v4.xlsx
+++ b/consultant_safe_v4/EBX_Q_템플릿_EM_추출·광물가공_중소_consultant_safe_v4.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="안내" sheetId="1" r:id="Red66bab5430347f3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EBX-Q 템플릿" sheetId="2" r:id="R1cb3f827cd7b49f9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="안내" sheetId="1" r:id="R46ebf4f6ad394915"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EBX-Q 템플릿" sheetId="2" r:id="Rb78985725b9a42f7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -640,10 +640,12 @@
         <x:v>일반 / 전략 (Strategy) / ESG 비전 및 중장기 전략</x:v>
       </x:c>
       <x:c r="P2" s="9" t="str">
-        <x:v>Use ESG report-ready Korean prose.
-Cover the relevant content slots before adding optional context.
-Prefer 4-6 sentences when evidence is sufficient; keep partial rows factual and bounded.
-Do not include source/page/reviewer/audit-trace wording in Final Answer.
+        <x:v>ROW-LEVEL OUTPUT RULES:
+1. Use ESG report-ready Korean prose, not reviewer/audit instructions.
+2. Cover the relevant content slots before adding optional context.
+3. Prefer 4-6 substantive sentences when evidence is sufficient; keep partial rows factual and bounded.
+4. Do not include source/page/PDF/reviewer/audit-trace wording in Final Answer.
+5. Do not include template/meta instructions such as estimation rules, reviewer guidance, or final wording guidance.
 Content Slots: • Disclosure item: ESG 비전 및 중장기 전략
 • Required material 1: 추진 배경·중요성
 • Required material 2: 정책·방침 선언
@@ -655,9 +657,12 @@
 • Do not convert these slots into a final sentence until company-specific facts are supplied.</x:v>
       </x:c>
       <x:c r="Q2" s="9" t="str">
-        <x:v>Final Answer may use company facts and supported figures only.
-Remove source names, source pages, PDF references, citation language, and reviewer follow-up wording.
-Do not invent figures, targets, organizations, certifications, incidents, or processes.
+        <x:v>FINAL ANSWER GUARDRAILS:
+1. Use company facts and supported figures only.
+2. Remove source names, source pages, PDF references, citation language, and reviewer follow-up wording.
+3. Do not invent figures, targets, organizations, certifications, incidents, or processes.
+4. Keep source/page/RAG trace only in metadata columns, never in Final Answer.
+5. Avoid raw OCR fragments or report headers; Final Answer should read like polished ESG report text.
 Style Options: • formal: ESG report tone; cover short qualitative facts with owner and evidence; suitable when source evidence is complete.
 • concise: 1-2 compact sentences; use when the company has limited evidence or the item only needs a factual status.
 • evidence-led: start with reporting period/source/scope, then explain the policy, activity, or metric; best for reviewer traceability.
@@ -673,14 +678,17 @@
 • Never copy 동종산업 references as wording; they are only topic/scope references.</x:v>
       </x:c>
       <x:c r="R2" s="9" t="str">
-        <x:v>SUFFICIENT: write a complete report paragraph with scope, governance/process, activity, and KPI or limitation where relevant.
-PARTIAL: disclose supported facts only and phrase missing data as a disclosure limitation, not as an audit note.
+        <x:v>COVERAGE HANDLING:
+SUFFICIENT: write a complete ESG report paragraph with scope, governance/process, activity, and KPI or business limitation where relevant.
+PARTIAL: disclose supported facts only and phrase missing data as a business disclosure limitation, not as an audit note.
 NO DATA: state that the company has not disclosed or has not yet managed the item, without source tracing.</x:v>
       </x:c>
       <x:c r="S2" s="9" t="str">
-        <x:v>When quantitative support exists, include period, unit, boundary, and trend if available.
-When quantitative support is unavailable, do not convert blanks, dashes, or missing values to zero.
-Keep metrics inside the report prose, not as source evidence notes.</x:v>
+        <x:v>METRIC HANDLING:
+1. When quantitative support exists, include period, unit, boundary, and trend if available.
+2. When quantitative support is unavailable, do not convert blanks, dashes, or missing values to zero.
+3. Keep metrics inside the report prose, not as source evidence notes.
+4. Do not write the rule itself in Final Answer; apply it silently.</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -753,10 +761,12 @@
         <x:v>일반 / 거버넌스 (Governance) / ESG 거버넌스 및 의사결정 체계</x:v>
       </x:c>
       <x:c r="P3" s="9" t="str">
-        <x:v>Use ESG report-ready Korean prose.
-Cover the relevant content slots before adding optional context.
-Prefer 4-6 sentences when evidence is sufficient; keep partial rows factual and bounded.
-Do not include source/page/reviewer/audit-trace wording in Final Answer.
+        <x:v>ROW-LEVEL OUTPUT RULES:
+1. Use ESG report-ready Korean prose, not reviewer/audit instructions.
+2. Cover the relevant content slots before adding optional context.
+3. Prefer 4-6 substantive sentences when evidence is sufficient; keep partial rows factual and bounded.
+4. Do not include source/page/PDF/reviewer/audit-trace wording in Final Answer.
+5. Do not include template/meta instructions such as estimation rules, reviewer guidance, or final wording guidance.
 Content Slots: • Disclosure item: ESG 거버넌스 및 의사결정 체계
 • Required material 1: 전담 조직·위원회 구성
 • Required material 2: 역할과 책임(R&amp;R)
@@ -768,9 +778,12 @@
 • Do not convert these slots into a final sentence until company-specific facts are supplied.</x:v>
       </x:c>
       <x:c r="Q3" s="9" t="str">
-        <x:v>Final Answer may use company facts and supported figures only.
-Remove source names, source pages, PDF references, citation language, and reviewer follow-up wording.
-Do not invent figures, targets, organizations, certifications, incidents, or processes.
+        <x:v>FINAL ANSWER GUARDRAILS:
+1. Use company facts and supported figures only.
+2. Remove source names, source pages, PDF references, citation language, and reviewer follow-up wording.
+3. Do not invent figures, targets, organizations, certifications, incidents, or processes.
+4. Keep source/page/RAG trace only in metadata columns, never in Final Answer.
+5. Avoid raw OCR fragments or report headers; Final Answer should read like polished ESG report text.
 Style Options: • formal: ESG report tone; cover short qualitative facts with owner and evidence; suitable when source evidence is complete.
 • concise: 1-2 compact sentences; use when the company has limited evidence or the item only needs a factual status.
 • evidence-led: start with reporting period/source/scope, then explain the policy, activity, or metric; best for reviewer traceability.
@@ -786,14 +799,17 @@
 • Never copy 동종산업 references as wording; they are only topic/scope references.</x:v>
       </x:c>
       <x:c r="R3" s="9" t="str">
-        <x:v>SUFFICIENT: write a complete report paragraph with scope, governance/process, activity, and KPI or limitation where relevant.
-PARTIAL: disclose supported facts only and phrase missing data as a disclosure limitation, not as an audit note.
+        <x:v>COVERAGE HANDLING:
+SUFFICIENT: write a complete ESG report paragraph with scope, governance/process, activity, and KPI or business limitation where relevant.
+PARTIAL: disclose supported facts only and phrase missing data as a business disclosure limitation, not as an audit note.
 NO DATA: state that the company has not disclosed or has not yet managed the item, without source tracing.</x:v>
       </x:c>
       <x:c r="S3" s="9" t="str">
-        <x:v>When quantitative support exists, include period, unit, boundary, and trend if available.
-When quantitative support is unavailable, do not convert blanks, dashes, or missing values to zero.
-Keep metrics inside the report prose, not as source evidence notes.</x:v>
+        <x:v>METRIC HANDLING:
+1. When quantitative support exists, include period, unit, boundary, and trend if available.
+2. When quantitative support is unavailable, do not convert blanks, dashes, or missing values to zero.
+3. Keep metrics inside the report prose, not as source evidence notes.
+4. Do not write the rule itself in Final Answer; apply it silently.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -866,10 +882,12 @@
         <x:v>일반 / 위험 관리 (Risk Management) / ESG 리스크 식별 및 관리 체계</x:v>
       </x:c>
       <x:c r="P4" s="9" t="str">
-        <x:v>Use ESG report-ready Korean prose.
-Cover the relevant content slots before adding optional context.
-Prefer 4-6 sentences when evidence is sufficient; keep partial rows factual and bounded.
-Do not include source/page/reviewer/audit-trace wording in Final Answer.
+        <x:v>ROW-LEVEL OUTPUT RULES:
+1. Use ESG report-ready Korean prose, not reviewer/audit instructions.
+2. Cover the relevant content slots before adding optional context.
+3. Prefer 4-6 substantive sentences when evidence is sufficient; keep partial rows factual and bounded.
+4. Do not include source/page/PDF/reviewer/audit-trace wording in Final Answer.
+5. Do not include template/meta instructions such as estimation rules, reviewer guidance, or final wording guidance.
 Content Slots: • Disclosure item: ESG 리스크 식별 및 관리 체계
 • Required material 1: 리스크 식별 절차
 • Required material 2: 평가·우선순위화
@@ -881,9 +899,12 @@
 • Do not convert these slots into a final sentence until company-specific facts are supplied.</x:v>
       </x:c>
       <x:c r="Q4" s="9" t="str">
-        <x:v>Final Answer may use company facts and supported figures only.
-Remove source names, source pages, PDF references, citation language, and reviewer follow-up wording.
-Do not invent figures, targets, organizations, certifications, incidents, or processes.
+        <x:v>FINAL ANSWER GUARDRAILS:
+1. Use company facts and supported figures only.
+2. Remove source names, source pages, PDF references, citation language, and reviewer follow-up wording.
+3. Do not invent figures, targets, organizations, certifications, incidents, or processes.
+4. Keep source/page/RAG trace only in metadata columns, never in Final Answer.
+5. Avoid raw OCR fragments or report headers; Final Answer should read like polished ESG report text.
 Style Options: • formal: ESG report tone; cover short qualitative facts with owner and evidence; suitable when source evidence is complete.
 • concise: 1-2 compact sentences; use when the company has limited evidence or the item only needs a factual status.
 • evidence-led: start with reporting period/source/scope, then explain the policy, activity, or metric; best for reviewer traceability.
@@ -899,14 +920,17 @@
 • Never copy 동종산업 references as wording; they are only topic/scope references.</x:v>
       </x:c>
       <x:c r="R4" s="9" t="str">
-        <x:v>SUFFICIENT: write a complete report paragraph with scope, governance/process, activity, and KPI or limitation where relevant.
-PARTIAL: disclose supported facts only and phrase missing data as a disclosure limitation, not as an audit note.
+        <x:v>COVERAGE HANDLING:
+SUFFICIENT: write a complete ESG report paragraph with scope, governance/process, activity, and KPI or business limitation where relevant.
+PARTIAL: disclose supported facts only and phrase missing data as a business disclosure limitation, not as an audit note.
 NO DATA: state that the company has not disclosed or has not yet managed the item, without source tracing.</x:v>
       </x:c>
       <x:c r="S4" s="9" t="str">
-        <x:v>When quantitative support exists, include period, unit, boundary, and trend if available.
-When quantitative support is unavailable, do not convert blanks, dashes, or missing values to zero.
-Keep metrics inside the report prose, not as source evidence notes.</x:v>
+        <x:v>METRIC HANDLING:
+1. When quantitative support exists, include period, unit, boundary, and trend if available.
+2. When quantitative support is unavailable, do not convert blanks, dashes, or missing values to zero.
+3. Keep metrics inside the report prose, not as source evidence notes.
+4. Do not write the rule itself in Final Answer; apply it silently.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -979,10 +1003,12 @@
         <x:v>사회 / 전략 (Strategy) / 안전보건 정책 및 목표</x:v>
       </x:c>
       <x:c r="P5" s="9" t="str">
-        <x:v>Use ESG report-ready Korean prose.
-Cover the relevant content slots before adding optional context.
-Prefer 4-6 sentences when evidence is sufficient; keep partial rows factual and bounded.
-Do not include source/page/reviewer/audit-trace wording in Final Answer.
+        <x:v>ROW-LEVEL OUTPUT RULES:
+1. Use ESG report-ready Korean prose, not reviewer/audit instructions.
+2. Cover the relevant content slots before adding optional context.
+3. Prefer 4-6 substantive sentences when evidence is sufficient; keep partial rows factual and bounded.
+4. Do not include source/page/PDF/reviewer/audit-trace wording in Final Answer.
+5. Do not include template/meta instructions such as estimation rules, reviewer guidance, or final wording guidance.
 Content Slots: • Disclosure item: 안전보건 정책 및 목표
 • Required material 1: 추진 배경·중요성
 • Required material 2: 정책·방침 선언
@@ -994,9 +1020,12 @@
 • Do not convert these slots into a final sentence until company-specific facts are supplied.</x:v>
       </x:c>
       <x:c r="Q5" s="9" t="str">
-        <x:v>Final Answer may use company facts and supported figures only.
-Remove source names, source pages, PDF references, citation language, and reviewer follow-up wording.
-Do not invent figures, targets, organizations, certifications, incidents, or processes.
+        <x:v>FINAL ANSWER GUARDRAILS:
+1. Use company facts and supported figures only.
+2. Remove source names, source pages, PDF references, citation language, and reviewer follow-up wording.
+3. Do not invent figures, targets, organizations, certifications, incidents, or processes.
+4. Keep source/page/RAG trace only in metadata columns, never in Final Answer.
+5. Avoid raw OCR fragments or report headers; Final Answer should read like polished ESG report text.
 Style Options: • formal: ESG report tone; cover short qualitative facts with owner and evidence; suitable when source evidence is complete.
 • concise: 1-2 compact sentences; use when the company has limited evidence or the item only needs a factual status.
 • evidence-led: start with reporting period/source/scope, then explain the policy, activity, or metric; best for reviewer traceability.
@@ -1012,14 +1041,17 @@
 • Never copy 동종산업 references as wording; they are only topic/scope references.</x:v>
       </x:c>
       <x:c r="R5" s="9" t="str">
-        <x:v>SUFFICIENT: write a complete report paragraph with scope, governance/process, activity, and KPI or limitation where relevant.
-PARTIAL: disclose supported facts only and phrase missing data as a disclosure limitation, not as an audit note.
+        <x:v>COVERAGE HANDLING:
+SUFFICIENT: write a complete ESG report paragraph with scope, governance/process, activity, and KPI or business limitation where relevant.
+PARTIAL: disclose supported facts only and phrase missing data as a business disclosure limitation, not as an audit note.
 NO DATA: state that the company has not disclosed or has not yet managed the item, without source tracing.</x:v>
       </x:c>
       <x:c r="S5" s="9" t="str">
-        <x:v>When quantitative support exists, include period, unit, boundary, and trend if available.
-When quantitative support is unavailable, do not convert blanks, dashes, or missing values to zero.
-Keep metrics inside the report prose, not as source evidence notes.</x:v>
+        <x:v>METRIC HANDLING:
+1. When quantitative support exists, include period, unit, boundary, and trend if available.
+2. When quantitative support is unavailable, do not convert blanks, dashes, or missing values to zero.
+3. Keep metrics inside the report prose, not as source evidence notes.
+4. Do not write the rule itself in Final Answer; apply it silently.</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -1092,10 +1124,12 @@
         <x:v>사회 / 거버넌스 (Governance) / 안전보건 관리 조직 및 책임</x:v>
       </x:c>
       <x:c r="P6" s="9" t="str">
-        <x:v>Use ESG report-ready Korean prose.
-Cover the relevant content slots before adding optional context.
-Prefer 4-6 sentences when evidence is sufficient; keep partial rows factual and bounded.
-Do not include source/page/reviewer/audit-trace wording in Final Answer.
+        <x:v>ROW-LEVEL OUTPUT RULES:
+1. Use ESG report-ready Korean prose, not reviewer/audit instructions.
+2. Cover the relevant content slots before adding optional context.
+3. Prefer 4-6 substantive sentences when evidence is sufficient; keep partial rows factual and bounded.
+4. Do not include source/page/PDF/reviewer/audit-trace wording in Final Answer.
+5. Do not include template/meta instructions such as estimation rules, reviewer guidance, or final wording guidance.
 Content Slots: • Disclosure item: 안전보건 관리 조직 및 책임
 • Required material 1: 전담 조직·위원회 구성
 • Required material 2: 역할과 책임(R&amp;R)
@@ -1107,9 +1141,12 @@
 • Do not convert these slots into a final sentence until company-specific facts are supplied.</x:v>
       </x:c>
       <x:c r="Q6" s="9" t="str">
-        <x:v>Final Answer may use company facts and supported figures only.
-Remove source names, source pages, PDF references, citation language, and reviewer follow-up wording.
-Do not invent figures, targets, organizations, certifications, incidents, or processes.
+        <x:v>FINAL ANSWER GUARDRAILS:
+1. Use company facts and supported figures only.
+2. Remove source names, source pages, PDF references, citation language, and reviewer follow-up wording.
+3. Do not invent figures, targets, organizations, certifications, incidents, or processes.
+4. Keep source/page/RAG trace only in metadata columns, never in Final Answer.
+5. Avoid raw OCR fragments or report headers; Final Answer should read like polished ESG report text.
 Style Options: • formal: ESG report tone; cover short qualitative facts with owner and evidence; suitable when source evidence is complete.
 • concise: 1-2 compact sentences; use when the company has limited evidence or the item only needs a factual status.
 • evidence-led: start with reporting period/source/scope, then explain the policy, activity, or metric; best for reviewer traceability.
@@ -1125,14 +1162,17 @@
 • Never copy 동종산업 references as wording; they are only topic/scope references.</x:v>
       </x:c>
       <x:c r="R6" s="9" t="str">
-        <x:v>SUFFICIENT: write a complete report paragraph with scope, governance/process, activity, and KPI or limitation where relevant.
-PARTIAL: disclose supported facts only and phrase missing data as a disclosure limitation, not as an audit note.
+        <x:v>COVERAGE HANDLING:
+SUFFICIENT: write a complete ESG report paragraph with scope, governance/process, activity, and KPI or business limitation where relevant.
+PARTIAL: disclose supported facts only and phrase missing data as a business disclosure limitation, not as an audit note.
 NO DATA: state that the company has not disclosed or has not yet managed the item, without source tracing.</x:v>
       </x:c>
       <x:c r="S6" s="9" t="str">
-        <x:v>When quantitative support exists, include period, unit, boundary, and trend if available.
-When quantitative support is unavailable, do not convert blanks, dashes, or missing values to zero.
-Keep metrics inside the report prose, not as source evidence notes.</x:v>
+        <x:v>METRIC HANDLING:
+1. When quantitative support exists, include period, unit, boundary, and trend if available.
+2. When quantitative support is unavailable, do not convert blanks, dashes, or missing values to zero.
+3. Keep metrics inside the report prose, not as source evidence notes.
+4. Do not write the rule itself in Final Answer; apply it silently.</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -1205,10 +1245,12 @@
         <x:v>사회 / 위험 관리 (Risk Management) / 산업안전 리스크 식별 및 예방 활동</x:v>
       </x:c>
       <x:c r="P7" s="9" t="str">
-        <x:v>Use ESG report-ready Korean prose.
-Cover the relevant content slots before adding optional context.
-Prefer 4-6 sentences when evidence is sufficient; keep partial rows factual and bounded.
-Do not include source/page/reviewer/audit-trace wording in Final Answer.
+        <x:v>ROW-LEVEL OUTPUT RULES:
+1. Use ESG report-ready Korean prose, not reviewer/audit instructions.
+2. Cover the relevant content slots before adding optional context.
+3. Prefer 4-6 substantive sentences when evidence is sufficient; keep partial rows factual and bounded.
+4. Do not include source/page/PDF/reviewer/audit-trace wording in Final Answer.
+5. Do not include template/meta instructions such as estimation rules, reviewer guidance, or final wording guidance.
 Content Slots: • Disclosure item: 산업안전 리스크 식별 및 예방 활동
 • Required material 1: 리스크 식별 절차
 • Required material 2: 평가·우선순위화
@@ -1220,9 +1262,12 @@
 • Do not convert these slots into a final sentence until company-specific facts are supplied.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str">
-        <x:v>Final Answer may use company facts and supported figures only.
-Remove source names, source pages, PDF references, citation language, and reviewer follow-up wording.
-Do not invent figures, targets, organizations, certifications, incidents, or processes.
+        <x:v>FINAL ANSWER GUARDRAILS:
+1. Use company facts and supported figures only.
+2. Remove source names, source pages, PDF references, citation language, and reviewer follow-up wording.
+3. Do not invent figures, targets, organizations, certifications, incidents, or processes.
+4. Keep source/page/RAG trace only in metadata columns, never in Final Answer.
+5. Avoid raw OCR fragments or report headers; Final Answer should read like polished ESG report text.
 Style Options: • formal: ESG report tone; cover short qualitative facts with owner and evidence; suitable when source evidence is complete.
 • concise: 1-2 compact sentences; use when the company has limited evidence or the item only needs a factual status.
 • evidence-led: start with reporting period/source/scope, then explain the policy, activity, or metric; best for reviewer traceability.
@@ -1238,14 +1283,17 @@
 • Never copy 동종산업 references as wording; they are only topic/scope references.</x:v>
       </x:c>
       <x:c r="R7" s="9" t="str">
-        <x:v>SUFFICIENT: write a complete report paragraph with scope, governance/process, activity, and KPI or limitation where relevant.
-PARTIAL: disclose supported facts only and phrase missing data as a disclosure limitation, not as an audit note.
+        <x:v>COVERAGE HANDLING:
+SUFFICIENT: write a complete ESG report paragraph with scope, governance/process, activity, and KPI or business limitation where relevant.
+PARTIAL: disclose supported facts only and phrase missing data as a business disclosure limitation, not as an audit note.
 NO DATA: state that the company has not disclosed or has not yet managed the item, without source tracing.</x:v>
       </x:c>
       <x:c r="S7" s="9" t="str">
-        <x:v>When quantitative support exists, include period, unit, boundary, and trend if available.
-When quantitative support is unavailable, do not convert blanks, dashes, or missing values to zero.
-Keep metrics inside the report prose, not as source evidence notes.</x:v>
+        <x:v>METRIC HANDLING:
+1. When quantitative support exists, include period, unit, boundary, and trend if available.
+2. When quantitative support is unavailable, do not convert blanks, dashes, or missing values to zero.
+3. Keep metrics inside the report prose, not as source evidence notes.
+4. Do not write the rule itself in Final Answer; apply it silently.</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -1321,10 +1369,12 @@
         <x:v>사회 / 지표 (Metrics) / 산업재해 발생 현황 및 안전 성과 지표</x:v>
       </x:c>
       <x:c r="P8" s="9" t="str">
-        <x:v>Use ESG report-ready Korean prose.
-Cover the relevant content slots before adding optional context.
-Prefer 4-6 sentences when evidence is sufficient; keep partial rows factual and bounded.
-Do not include source/page/reviewer/audit-trace wording in Final Answer.
+        <x:v>ROW-LEVEL OUTPUT RULES:
+1. Use ESG report-ready Korean prose, not reviewer/audit instructions.
+2. Cover the relevant content slots before adding optional context.
+3. Prefer 4-6 substantive sentences when evidence is sufficient; keep partial rows factual and bounded.
+4. Do not include source/page/PDF/reviewer/audit-trace wording in Final Answer.
+5. Do not include template/meta instructions such as estimation rules, reviewer guidance, or final wording guidance.
 Content Slots: • Disclosure item: 산업재해 발생 현황 및 안전 성과 지표
 • Required material 1: 핵심 성과지표(KPI) 정의
 • Required material 2: 최근 실적 수치
@@ -1337,9 +1387,12 @@
 • Do not convert these slots into a final sentence until company-specific facts are supplied.</x:v>
       </x:c>
       <x:c r="Q8" s="9" t="str">
-        <x:v>Final Answer may use company facts and supported figures only.
-Remove source names, source pages, PDF references, citation language, and reviewer follow-up wording.
-Do not invent figures, targets, organizations, certifications, incidents, or processes.
+        <x:v>FINAL ANSWER GUARDRAILS:
+1. Use company facts and supported figures only.
+2. Remove source names, source pages, PDF references, citation language, and reviewer follow-up wording.
+3. Do not invent figures, targets, organizations, certifications, incidents, or processes.
+4. Keep source/page/RAG trace only in metadata columns, never in Final Answer.
+5. Avoid raw OCR fragments or report headers; Final Answer should read like polished ESG report text.
 Style Options: • formal: ESG report tone; cover short qualitative facts with owner and evidence; suitable when source evidence is complete.
 • concise: 1-2 compact sentences; use when the company has limited evidence or the item only needs a factual status.
 • evidence-led: start with period, boundary, unit, and source system, then state value/status; if unavailable, state 미집계/해당사항 없음.
@@ -1355,14 +1408,17 @@
 • Never copy 동종산업 references as wording; they are only topic/scope references.</x:v>
       </x:c>
       <x:c r="R8" s="9" t="str">
-        <x:v>SUFFICIENT: write a complete report paragraph with scope, governance/process, activity, and KPI or limitation where relevant.
-PARTIAL: disclose supported facts only and phrase missing data as a disclosure limitation, not as an audit note.
+        <x:v>COVERAGE HANDLING:
+SUFFICIENT: write a complete ESG report paragraph with scope, governance/process, activity, and KPI or business limitation where relevant.
+PARTIAL: disclose supported facts only and phrase missing data as a business disclosure limitation, not as an audit note.
 NO DATA: state that the company has not disclosed or has not yet managed the item, without source tracing.</x:v>
       </x:c>
       <x:c r="S8" s="9" t="str">
-        <x:v>When quantitative support exists, include period, unit, boundary, and trend if available.
-When quantitative support is unavailable, do not convert blanks, dashes, or missing values to zero.
-Keep metrics inside the report prose, not as source evidence notes.</x:v>
+        <x:v>METRIC HANDLING:
+1. When quantitative support exists, include period, unit, boundary, and trend if available.
+2. When quantitative support is unavailable, do not convert blanks, dashes, or missing values to zero.
+3. Keep metrics inside the report prose, not as source evidence notes.
+4. Do not write the rule itself in Final Answer; apply it silently.</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -1435,10 +1491,12 @@
         <x:v>사회 / 전략 (Strategy) / 인권경영 정책 및 목표</x:v>
       </x:c>
       <x:c r="P9" s="9" t="str">
-        <x:v>Use ESG report-ready Korean prose.
-Cover the relevant content slots before adding optional context.
-Prefer 4-6 sentences when evidence is sufficient; keep partial rows factual and bounded.
-Do not include source/page/reviewer/audit-trace wording in Final Answer.
+        <x:v>ROW-LEVEL OUTPUT RULES:
+1. Use ESG report-ready Korean prose, not reviewer/audit instructions.
+2. Cover the relevant content slots before adding optional context.
+3. Prefer 4-6 substantive sentences when evidence is sufficient; keep partial rows factual and bounded.
+4. Do not include source/page/PDF/reviewer/audit-trace wording in Final Answer.
+5. Do not include template/meta instructions such as estimation rules, reviewer guidance, or final wording guidance.
 Content Slots: • Disclosure item: 인권경영 정책 및 목표
 • Required material 1: 추진 배경·중요성
 • Required material 2: 정책·방침 선언
@@ -1450,9 +1508,12 @@
 • Do not convert these slots into a final sentence until company-specific facts are supplied.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str">
-        <x:v>Final Answer may use company facts and supported figures only.
-Remove source names, source pages, PDF references, citation language, and reviewer follow-up wording.
-Do not invent figures, targets, organizations, certifications, incidents, or processes.
+        <x:v>FINAL ANSWER GUARDRAILS:
+1. Use company facts and supported figures only.
+2. Remove source names, source pages, PDF references, citation language, and reviewer follow-up wording.
+3. Do not invent figures, targets, organizations, certifications, incidents, or processes.
+4. Keep source/page/RAG trace only in metadata columns, never in Final Answer.
+5. Avoid raw OCR fragments or report headers; Final Answer should read like polished ESG report text.
 Style Options: • formal: ESG report tone; cover short qualitative facts with owner and evidence; suitable when source evidence is complete.
 • concise: 1-2 compact sentences; use when the company has limited evidence or the item only needs a factual status.
 • evidence-led: start with reporting period/source/scope, then explain the policy, activity, or metric; best for reviewer traceability.
@@ -1468,14 +1529,17 @@
 • Never copy 동종산업 references as wording; they are only topic/scope references.</x:v>
       </x:c>
       <x:c r="R9" s="9" t="str">
-        <x:v>SUFFICIENT: write a complete report paragraph with scope, governance/process, activity, and KPI or limitation where relevant.
-PARTIAL: disclose supported facts only and phrase missing data as a disclosure limitation, not as an audit note.
+        <x:v>COVERAGE HANDLING:
+SUFFICIENT: write a complete ESG report paragraph with scope, governance/process, activity, and KPI or business limitation where relevant.
+PARTIAL: disclose supported facts only and phrase missing data as a business disclosure limitation, not as an audit note.
 NO DATA: state that the company has not disclosed or has not yet managed the item, without source tracing.</x:v>
       </x:c>
       <x:c r="S9" s="9" t="str">
-        <x:v>When quantitative support exists, include period, unit, boundary, and trend if available.
-When quantitative support is unavailable, do not convert blanks, dashes, or missing values to zero.
-Keep metrics inside the report prose, not as source evidence notes.</x:v>
+        <x:v>METRIC HANDLING:
+1. When quantitative support exists, include period, unit, boundary, and trend if available.
+2. When quantitative support is unavailable, do not convert blanks, dashes, or missing values to zero.
+3. Keep metrics inside the report prose, not as source evidence notes.
+4. Do not write the rule itself in Final Answer; apply it silently.</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -1548,10 +1612,12 @@
         <x:v>사회 / 거버넌스 (Governance) / 노동 및 인권 관리 체계</x:v>
       </x:c>
       <x:c r="P10" s="9" t="str">
-        <x:v>Use ESG report-ready Korean prose.
-Cover the relevant content slots before adding optional context.
-Prefer 4-6 sentences when evidence is sufficient; keep partial rows factual and bounded.
-Do not include source/page/reviewer/audit-trace wording in Final Answer.
+        <x:v>ROW-LEVEL OUTPUT RULES:
+1. Use ESG report-ready Korean prose, not reviewer/audit instructions.
+2. Cover the relevant content slots before adding optional context.
+3. Prefer 4-6 substantive sentences when evidence is sufficient; keep partial rows factual and bounded.
+4. Do not include source/page/PDF/reviewer/audit-trace wording in Final Answer.
+5. Do not include template/meta instructions such as estimation rules, reviewer guidance, or final wording guidance.
 Content Slots: • Disclosure item: 노동 및 인권 관리 체계
 • Required material 1: 전담 조직·위원회 구성
 • Required material 2: 역할과 책임(R&amp;R)
@@ -1563,9 +1629,12 @@
 • Do not convert these slots into a final sentence until company-specific facts are supplied.</x:v>
       </x:c>
       <x:c r="Q10" s="9" t="str">
-        <x:v>Final Answer may use company facts and supported figures only.
-Remove source names, source pages, PDF references, citation language, and reviewer follow-up wording.
-Do not invent figures, targets, organizations, certifications, incidents, or processes.
+        <x:v>FINAL ANSWER GUARDRAILS:
+1. Use company facts and supported figures only.
+2. Remove source names, source pages, PDF references, citation language, and reviewer follow-up wording.
+3. Do not invent figures, targets, organizations, certifications, incidents, or processes.
+4. Keep source/page/RAG trace only in metadata columns, never in Final Answer.
+5. Avoid raw OCR fragments or report headers; Final Answer should read like polished ESG report text.
 Style Options: • formal: ESG report tone; cover short qualitative facts with owner and evidence; suitable when source evidence is complete.
 • concise: 1-2 compact sentences; use when the company has limited evidence or the item only needs a factual status.
 • evidence-led: start with period, boundary, unit, and source system, then state value/status; if unavailable, state 미집계/해당사항 없음.
@@ -1581,14 +1650,17 @@
 • Never copy 동종산업 references as wording; they are only topic/scope references.</x:v>
       </x:c>
       <x:c r="R10" s="9" t="str">
-        <x:v>SUFFICIENT: write a complete report paragraph with scope, governance/process, activity, and KPI or limitation where relevant.
-PARTIAL: disclose supported facts only and phrase missing data as a disclosure limitation, not as an audit note.
+        <x:v>COVERAGE HANDLING:
+SUFFICIENT: write a complete ESG report paragraph with scope, governance/process, activity, and KPI or business limitation where relevant.
+PARTIAL: disclose supported facts only and phrase missing data as a business disclosure limitation, not as an audit note.
 NO DATA: state that the company has not disclosed or has not yet managed the item, without source tracing.</x:v>
       </x:c>
       <x:c r="S10" s="9" t="str">
-        <x:v>When quantitative support exists, include period, unit, boundary, and trend if available.
-When quantitative support is unavailable, do not convert blanks, dashes, or missing values to zero.
-Keep metrics inside the report prose, not as source evidence notes.</x:v>
+        <x:v>METRIC HANDLING:
+1. When quantitative support exists, include period, unit, boundary, and trend if available.
+2. When quantitative support is unavailable, do not convert blanks, dashes, or missing values to zero.
+3. Keep metrics inside the report prose, not as source evidence notes.
+4. Do not write the rule itself in Final Answer; apply it silently.</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -1661,10 +1733,12 @@
         <x:v>사회 / 위험 관리 (Risk Management) / 인권 리스크 식별 및 대응 활동</x:v>
       </x:c>
       <x:c r="P11" s="9" t="str">
-        <x:v>Use ESG report-ready Korean prose.
-Cover the relevant content slots before adding optional context.
-Prefer 4-6 sentences when evidence is sufficient; keep partial rows factual and bounded.
-Do not include source/page/reviewer/audit-trace wording in Final Answer.
+        <x:v>ROW-LEVEL OUTPUT RULES:
+1. Use ESG report-ready Korean prose, not reviewer/audit instructions.
+2. Cover the relevant content slots before adding optional context.
+3. Prefer 4-6 substantive sentences when evidence is sufficient; keep partial rows factual and bounded.
+4. Do not include source/page/PDF/reviewer/audit-trace wording in Final Answer.
+5. Do not include template/meta instructions such as estimation rules, reviewer guidance, or final wording guidance.
 Content Slots: • Disclosure item: 인권 리스크 식별 및 대응 활동
 • Required material 1: 리스크 식별 절차
 • Required material 2: 평가·우선순위화
@@ -1676,9 +1750,12 @@
 • Do not convert these slots into a final sentence until company-specific facts are supplied.</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str">
-        <x:v>Final Answer may use company facts and supported figures only.
-Remove source names, source pages, PDF references, citation language, and reviewer follow-up wording.
-Do not invent figures, targets, organizations, certifications, incidents, or processes.
+        <x:v>FINAL ANSWER GUARDRAILS:
+1. Use company facts and supported figures only.
+2. Remove source names, source pages, PDF references, citation language, and reviewer follow-up wording.
+3. Do not invent figures, targets, organizations, certifications, incidents, or processes.
+4. Keep source/page/RAG trace only in metadata columns, never in Final Answer.
+5. Avoid raw OCR fragments or report headers; Final Answer should read like polished ESG report text.
 Style Options: • formal: ESG report tone; cover short qualitative facts with owner and evidence; suitable when source evidence is complete.
 • concise: 1-2 compact sentences; use when the company has limited evidence or the item only needs a factual status.
 • evidence-led: start with reporting period/source/scope, then explain the policy, activity, or metric; best for reviewer traceability.
@@ -1694,14 +1771,17 @@
 • Never copy 동종산업 references as wording; they are only topic/scope references.</x:v>
       </x:c>
       <x:c r="R11" s="9" t="str">
-        <x:v>SUFFICIENT: write a complete report paragraph with scope, governance/process, activity, and KPI or limitation where relevant.
-PARTIAL: disclose supported facts only and phrase missing data as a disclosure limitation, not as an audit note.
+        <x:v>COVERAGE HANDLING:
+SUFFICIENT: write a complete ESG report paragraph with scope, governance/process, activity, and KPI or business limitation where relevant.
+PARTIAL: disclose supported facts only and phrase missing data as a business disclosure limitation, not as an audit note.
 NO DATA: state that the company has not disclosed or has not yet managed the item, without source tracing.</x:v>
       </x:c>
       <x:c r="S11" s="9" t="str">
-        <x:v>When quantitative support exists, include period, unit, boundary, and trend if available.
-When quantitative support is unavailable, do not convert blanks, dashes, or missing values to zero.
-Keep metrics inside the report prose, not as source evidence notes.</x:v>
+        <x:v>METRIC HANDLING:
+1. When quantitative support exists, include period, unit, boundary, and trend if available.
+2. When quantitative support is unavailable, do not convert blanks, dashes, or missing values to zero.
+3. Keep metrics inside the report prose, not as source evidence notes.
+4. Do not write the rule itself in Final Answer; apply it silently.</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -1777,10 +1857,12 @@
         <x:v>사회 / 지표 (Metrics) / 인권 관련 고충 및 처리 현황</x:v>
       </x:c>
       <x:c r="P12" s="9" t="str">
-        <x:v>Use ESG report-ready Korean prose.
-Cover the relevant content slots before adding optional context.
-Prefer 4-6 sentences when evidence is sufficient; keep partial rows factual and bounded.
-Do not include source/page/reviewer/audit-trace wording in Final Answer.
+        <x:v>ROW-LEVEL OUTPUT RULES:
+1. Use ESG report-ready Korean prose, not reviewer/audit instructions.
+2. Cover the relevant content slots before adding optional context.
+3. Prefer 4-6 substantive sentences when evidence is sufficient; keep partial rows factual and bounded.
+4. Do not include source/page/PDF/reviewer/audit-trace wording in Final Answer.
+5. Do not include template/meta instructions such as estimation rules, reviewer guidance, or final wording guidance.
 Content Slots: • Disclosure item: 인권 관련 고충 및 처리 현황
 • Required material 1: 핵심 성과지표(KPI) 정의
 • Required material 2: 최근 실적 수치
@@ -1793,9 +1875,12 @@
 • Do not convert these slots into a final sentence until company-specific facts are supplied.</x:v>
       </x:c>
       <x:c r="Q12" s="9" t="str">
-        <x:v>Final Answer may use company facts and supported figures only.
-Remove source names, source pages, PDF references, citation language, and reviewer follow-up wording.
-Do not invent figures, targets, organizations, certifications, incidents, or processes.
+        <x:v>FINAL ANSWER GUARDRAILS:
+1. Use company facts and supported figures only.
+2. Remove source names, source pages, PDF references, citation language, and reviewer follow-up wording.
+3. Do not invent figures, targets, organizations, certifications, incidents, or processes.
+4. Keep source/page/RAG trace only in metadata columns, never in Final Answer.
+5. Avoid raw OCR fragments or report headers; Final Answer should read like polished ESG report text.
 Style Options: • formal: ESG report tone; cover short qualitative facts with owner and evidence; suitable when source evidence is complete.
 • concise: 1-2 compact sentences; use when the company has limited evidence or the item only needs a factual status.
 • evidence-led: start with period, boundary, unit, and source system, then state value/status; if unavailable, state 미집계/해당사항 없음.
@@ -1811,14 +1896,17 @@
 • Never copy 동종산업 references as wording; they are only topic/scope references.</x:v>
       </x:c>
       <x:c r="R12" s="9" t="str">
-        <x:v>SUFFICIENT: write a complete report paragraph with scope, governance/process, activity, and KPI or limitation where relevant.
-PARTIAL: disclose supported facts only and phrase missing data as a disclosure limitation, not as an audit note.
+        <x:v>COVERAGE HANDLING:
+SUFFICIENT: write a complete ESG report paragraph with scope, governance/process, activity, and KPI or business limitation where relevant.
+PARTIAL: disclose supported facts only and phrase missing data as a business disclosure limitation, not as an audit note.
 NO DATA: state that the company has not disclosed or has not yet managed the item, without source tracing.</x:v>
       </x:c>
       <x:c r="S12" s="9" t="str">
-        <x:v>When quantitative support exists, include period, unit, boundary, and trend if available.
-When quantitative support is unavailable, do not convert blanks, dashes, or missing values to zero.
-Keep metrics inside the report prose, not as source evidence notes.</x:v>
+        <x:v>METRIC HANDLING:
+1. When quantitative support exists, include period, unit, boundary, and trend if available.
+2. When quantitative support is unavailable, do not convert blanks, dashes, or missing values to zero.
+3. Keep metrics inside the report prose, not as source evidence notes.
+4. Do not write the rule itself in Final Answer; apply it silently.</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -1891,10 +1979,12 @@
         <x:v>사회 / 전략 (Strategy) / 제품 안전 및 품질 관리 정책</x:v>
       </x:c>
       <x:c r="P13" s="9" t="str">
-        <x:v>Use ESG report-ready Korean prose.
-Cover the relevant content slots before adding optional context.
-Prefer 4-6 sentences when evidence is sufficient; keep partial rows factual and bounded.
-Do not include source/page/reviewer/audit-trace wording in Final Answer.
+        <x:v>ROW-LEVEL OUTPUT RULES:
+1. Use ESG report-ready Korean prose, not reviewer/audit instructions.
+2. Cover the relevant content slots before adding optional context.
+3. Prefer 4-6 substantive sentences when evidence is sufficient; keep partial rows factual and bounded.
+4. Do not include source/page/PDF/reviewer/audit-trace wording in Final Answer.
+5. Do not include template/meta instructions such as estimation rules, reviewer guidance, or final wording guidance.
 Content Slots: • Disclosure item: 제품 안전 및 품질 관리 정책
 • Required material 1: 추진 배경·중요성
 • Required material 2: 정책·방침 선언
@@ -1906,9 +1996,12 @@
 • Do not convert these slots into a final sentence until company-specific facts are supplied.</x:v>
       </x:c>
       <x:c r="Q13" s="9" t="str">
-        <x:v>Final Answer may use company facts and supported figures only.
-Remove source names, source pages, PDF references, citation language, and reviewer follow-up wording.
-Do not invent figures, targets, organizations, certifications, incidents, or processes.
+        <x:v>FINAL ANSWER GUARDRAILS:
+1. Use company facts and supported figures only.
+2. Remove source names, source pages, PDF references, citation language, and reviewer follow-up wording.
+3. Do not invent figures, targets, organizations, certifications, incidents, or processes.
+4. Keep source/page/RAG trace only in metadata columns, never in Final Answer.
+5. Avoid raw OCR fragments or report headers; Final Answer should read like polished ESG report text.
 Style Options: • formal: ESG report tone; cover short qualitative facts with owner and evidence; suitable when source evidence is complete.
 • concise: 1-2 compact sentences; use when the company has limited evidence or the item only needs a factual status.
 • evidence-led: start with period, boundary, unit, and source system, then state value/status; if unavailable, state 미집계/해당사항 없음.
@@ -1924,14 +2017,17 @@
 • Never copy 동종산업 references as wording; they are only topic/scope references.</x:v>
       </x:c>
       <x:c r="R13" s="9" t="str">
-        <x:v>SUFFICIENT: write a complete report paragraph with scope, governance/process, activity, and KPI or limitation where relevant.
-PARTIAL: disclose supported facts only and phrase missing data as a disclosure limitation, not as an audit note.
+        <x:v>COVERAGE HANDLING:
+SUFFICIENT: write a complete ESG report paragraph with scope, governance/process, activity, and KPI or business limitation where relevant.
+PARTIAL: disclose supported facts only and phrase missing data as a business disclosure limitation, not as an audit note.
 NO DATA: state that the company has not disclosed or has not yet managed the item, without source tracing.</x:v>
       </x:c>
       <x:c r="S13" s="9" t="str">
-        <x:v>When quantitative support exists, include period, unit, boundary, and trend if available.
-When quantitative support is unavailable, do not convert blanks, dashes, or missing values to zero.
-Keep metrics inside the report prose, not as source evidence notes.</x:v>
+        <x:v>METRIC HANDLING:
+1. When quantitative support exists, include period, unit, boundary, and trend if available.
+2. When quantitative support is unavailable, do not convert blanks, dashes, or missing values to zero.
+3. Keep metrics inside the report prose, not as source evidence notes.
+4. Do not write the rule itself in Final Answer; apply it silently.</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -2004,10 +2100,12 @@
         <x:v>사회 / 거버넌스 (Governance) / 품질 관리 조직 및 책임</x:v>
       </x:c>
       <x:c r="P14" s="9" t="str">
-        <x:v>Use ESG report-ready Korean prose.
-Cover the relevant content slots before adding optional context.
-Prefer 4-6 sentences when evidence is sufficient; keep partial rows factual and bounded.
-Do not include source/page/reviewer/audit-trace wording in Final Answer.
+        <x:v>ROW-LEVEL OUTPUT RULES:
+1. Use ESG report-ready Korean prose, not reviewer/audit instructions.
+2. Cover the relevant content slots before adding optional context.
+3. Prefer 4-6 substantive sentences when evidence is sufficient; keep partial rows factual and bounded.
+4. Do not include source/page/PDF/reviewer/audit-trace wording in Final Answer.
+5. Do not include template/meta instructions such as estimation rules, reviewer guidance, or final wording guidance.
 Content Slots: • Disclosure item: 품질 관리 조직 및 책임
 • Required material 1: 전담 조직·위원회 구성
 • Required material 2: 역할과 책임(R&amp;R)
@@ -2019,9 +2117,12 @@
 • Do not convert these slots into a final sentence until company-specific facts are supplied.</x:v>
       </x:c>
       <x:c r="Q14" s="9" t="str">
-        <x:v>Final Answer may use company facts and supported figures only.
-Remove source names, source pages, PDF references, citation language, and reviewer follow-up wording.
-Do not invent figures, targets, organizations, certifications, incidents, or processes.
+        <x:v>FINAL ANSWER GUARDRAILS:
+1. Use company facts and supported figures only.
+2. Remove source names, source pages, PDF references, citation language, and reviewer follow-up wording.
+3. Do not invent figures, targets, organizations, certifications, incidents, or processes.
+4. Keep source/page/RAG trace only in metadata columns, never in Final Answer.
+5. Avoid raw OCR fragments or report headers; Final Answer should read like polished ESG report text.
 Style Options: • formal: ESG report tone; cover short qualitative facts with owner and evidence; suitable when source evidence is complete.
 • concise: 1-2 compact sentences; use when the company has limited evidence or the item only needs a factual status.
 • evidence-led: start with reporting period/source/scope, then explain the policy, activity, or metric; best for reviewer traceability.
@@ -2037,14 +2138,17 @@
 • Never copy 동종산업 references as wording; they are only topic/scope references.</x:v>
       </x:c>
       <x:c r="R14" s="9" t="str">
-        <x:v>SUFFICIENT: write a complete report paragraph with scope, governance/process, activity, and KPI or limitation where relevant.
-PARTIAL: disclose supported facts only and phrase missing data as a disclosure limitation, not as an audit note.
+        <x:v>COVERAGE HANDLING:
+SUFFICIENT: write a complete ESG report paragraph with scope, governance/process, activity, and KPI or business limitation where relevant.
+PARTIAL: disclose supported facts only and phrase missing data as a business disclosure limitation, not as an audit note.
 NO DATA: state that the company has not disclosed or has not yet managed the item, without source tracing.</x:v>
       </x:c>
       <x:c r="S14" s="9" t="str">
-        <x:v>When quantitative support exists, include period, unit, boundary, and trend if available.
-When quantitative support is unavailable, do not convert blanks, dashes, or missing values to zero.
-Keep metrics inside the report prose, not as source evidence notes.</x:v>
+        <x:v>METRIC HANDLING:
+1. When quantitative support exists, include period, unit, boundary, and trend if available.
+2. When quantitative support is unavailable, do not convert blanks, dashes, or missing values to zero.
+3. Keep metrics inside the report prose, not as source evidence notes.
+4. Do not write the rule itself in Final Answer; apply it silently.</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -2117,10 +2221,12 @@
         <x:v>사회 / 위험 관리 (Risk Management) / 제품 품질 및 안전 리스크 관리</x:v>
       </x:c>
       <x:c r="P15" s="9" t="str">
-        <x:v>Use ESG report-ready Korean prose.
-Cover the relevant content slots before adding optional context.
-Prefer 4-6 sentences when evidence is sufficient; keep partial rows factual and bounded.
-Do not include source/page/reviewer/audit-trace wording in Final Answer.
+        <x:v>ROW-LEVEL OUTPUT RULES:
+1. Use ESG report-ready Korean prose, not reviewer/audit instructions.
+2. Cover the relevant content slots before adding optional context.
+3. Prefer 4-6 substantive sentences when evidence is sufficient; keep partial rows factual and bounded.
+4. Do not include source/page/PDF/reviewer/audit-trace wording in Final Answer.
+5. Do not include template/meta instructions such as estimation rules, reviewer guidance, or final wording guidance.
 Content Slots: • Disclosure item: 제품 품질 및 안전 리스크 관리
 • Required material 1: 리스크 식별 절차
 • Required material 2: 평가·우선순위화
@@ -2132,9 +2238,12 @@
 • Do not convert these slots into a final sentence until company-specific facts are supplied.</x:v>
       </x:c>
       <x:c r="Q15" s="9" t="str">
-        <x:v>Final Answer may use company facts and supported figures only.
-Remove source names, source pages, PDF references, citation language, and reviewer follow-up wording.
-Do not invent figures, targets, organizations, certifications, incidents, or processes.
+        <x:v>FINAL ANSWER GUARDRAILS:
+1. Use company facts and supported figures only.
+2. Remove source names, source pages, PDF references, citation language, and reviewer follow-up wording.
+3. Do not invent figures, targets, organizations, certifications, incidents, or processes.
+4. Keep source/page/RAG trace only in metadata columns, never in Final Answer.
+5. Avoid raw OCR fragments or report headers; Final Answer should read like polished ESG report text.
 Style Options: • formal: ESG report tone; cover short qualitative facts with owner and evidence; suitable when source evidence is complete.
 • concise: 1-2 compact sentences; use when the company has limited evidence or the item only needs a factual status.
 • evidence-led: start with reporting period/source/scope, then explain the policy, activity, or metric; best for reviewer traceability.
@@ -2150,14 +2259,17 @@
 • Never copy 동종산업 references as wording; they are only topic/scope references.</x:v>
       </x:c>
       <x:c r="R15" s="9" t="str">
-        <x:v>SUFFICIENT: write a complete report paragraph with scope, governance/process, activity, and KPI or limitation where relevant.
-PARTIAL: disclose supported facts only and phrase missing data as a disclosure limitation, not as an audit note.
+        <x:v>COVERAGE HANDLING:
+SUFFICIENT: write a complete ESG report paragraph with scope, governance/process, activity, and KPI or business limitation where relevant.
+PARTIAL: disclose supported facts only and phrase missing data as a business disclosure limitation, not as an audit note.
 NO DATA: state that the company has not disclosed or has not yet managed the item, without source tracing.</x:v>
       </x:c>
       <x:c r="S15" s="9" t="str">
-        <x:v>When quantitative support exists, include period, unit, boundary, and trend if available.
-When quantitative support is unavailable, do not convert blanks, dashes, or missing values to zero.
-Keep metrics inside the report prose, not as source evidence notes.</x:v>
+        <x:v>METRIC HANDLING:
+1. When quantitative support exists, include period, unit, boundary, and trend if available.
+2. When quantitative support is unavailable, do not convert blanks, dashes, or missing values to zero.
+3. Keep metrics inside the report prose, not as source evidence notes.
+4. Do not write the rule itself in Final Answer; apply it silently.</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -2233,10 +2345,12 @@
         <x:v>사회 / 지표 (Metrics) / 제품 안전 및 품질 관련 사고 현황</x:v>
       </x:c>
       <x:c r="P16" s="9" t="str">
-        <x:v>Use ESG report-ready Korean prose.
-Cover the relevant content slots before adding optional context.
-Prefer 4-6 sentences when evidence is sufficient; keep partial rows factual and bounded.
-Do not include source/page/reviewer/audit-trace wording in Final Answer.
+        <x:v>ROW-LEVEL OUTPUT RULES:
+1. Use ESG report-ready Korean prose, not reviewer/audit instructions.
+2. Cover the relevant content slots before adding optional context.
+3. Prefer 4-6 substantive sentences when evidence is sufficient; keep partial rows factual and bounded.
+4. Do not include source/page/PDF/reviewer/audit-trace wording in Final Answer.
+5. Do not include template/meta instructions such as estimation rules, reviewer guidance, or final wording guidance.
 Content Slots: • Disclosure item: 제품 안전 및 품질 관련 사고 현황
 • Required material 1: 핵심 성과지표(KPI) 정의
 • Required material 2: 최근 실적 수치
@@ -2249,9 +2363,12 @@
 • Do not convert these slots into a final sentence until company-specific facts are supplied.</x:v>
       </x:c>
       <x:c r="Q16" s="9" t="str">
-        <x:v>Final Answer may use company facts and supported figures only.
-Remove source names, source pages, PDF references, citation language, and reviewer follow-up wording.
-Do not invent figures, targets, organizations, certifications, incidents, or processes.
+        <x:v>FINAL ANSWER GUARDRAILS:
+1. Use company facts and supported figures only.
+2. Remove source names, source pages, PDF references, citation language, and reviewer follow-up wording.
+3. Do not invent figures, targets, organizations, certifications, incidents, or processes.
+4. Keep source/page/RAG trace only in metadata columns, never in Final Answer.
+5. Avoid raw OCR fragments or report headers; Final Answer should read like polished ESG report text.
 Style Options: • formal: ESG report tone; cover short qualitative facts with owner and evidence; suitable when source evidence is complete.
 • concise: 1-2 compact sentences; use when the company has limited evidence or the item only needs a factual status.
 • evidence-led: start with period, boundary, unit, and source system, then state value/status; if unavailable, state 미집계/해당사항 없음.
@@ -2267,14 +2384,17 @@
 • Never copy 동종산업 references as wording; they are only topic/scope references.</x:v>
       </x:c>
       <x:c r="R16" s="9" t="str">
-        <x:v>SUFFICIENT: write a complete report paragraph with scope, governance/process, activity, and KPI or limitation where relevant.
-PARTIAL: disclose supported facts only and phrase missing data as a disclosure limitation, not as an audit note.
+        <x:v>COVERAGE HANDLING:
+SUFFICIENT: write a complete ESG report paragraph with scope, governance/process, activity, and KPI or business limitation where relevant.
+PARTIAL: disclose supported facts only and phrase missing data as a business disclosure limitation, not as an audit note.
 NO DATA: state that the company has not disclosed or has not yet managed the item, without source tracing.</x:v>
       </x:c>
       <x:c r="S16" s="9" t="str">
-        <x:v>When quantitative support exists, include period, unit, boundary, and trend if available.
-When quantitative support is unavailable, do not convert blanks, dashes, or missing values to zero.
-Keep metrics inside the report prose, not as source evidence notes.</x:v>
+        <x:v>METRIC HANDLING:
+1. When quantitative support exists, include period, unit, boundary, and trend if available.
+2. When quantitative support is unavailable, do not convert blanks, dashes, or missing values to zero.
+3. Keep metrics inside the report prose, not as source evidence notes.
+4. Do not write the rule itself in Final Answer; apply it silently.</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -2347,10 +2467,12 @@
         <x:v>사회 / 전략 (Strategy) / 정보보안 및 개인정보 보호 정책</x:v>
       </x:c>
       <x:c r="P17" s="9" t="str">
-        <x:v>Use ESG report-ready Korean prose.
-Cover the relevant content slots before adding optional context.
-Prefer 4-6 sentences when evidence is sufficient; keep partial rows factual and bounded.
-Do not include source/page/reviewer/audit-trace wording in Final Answer.
+        <x:v>ROW-LEVEL OUTPUT RULES:
+1. Use ESG report-ready Korean prose, not reviewer/audit instructions.
+2. Cover the relevant content slots before adding optional context.
+3. Prefer 4-6 substantive sentences when evidence is sufficient; keep partial rows factual and bounded.
+4. Do not include source/page/PDF/reviewer/audit-trace wording in Final Answer.
+5. Do not include template/meta instructions such as estimation rules, reviewer guidance, or final wording guidance.
 Content Slots: • Disclosure item: 정보보안 및 개인정보 보호 정책
 • Required material 1: 추진 배경·중요성
 • Required material 2: 정책·방침 선언
@@ -2362,9 +2484,12 @@
 • Do not convert these slots into a final sentence until company-specific facts are supplied.</x:v>
       </x:c>
       <x:c r="Q17" s="9" t="str">
-        <x:v>Final Answer may use company facts and supported figures only.
-Remove source names, source pages, PDF references, citation language, and reviewer follow-up wording.
-Do not invent figures, targets, organizations, certifications, incidents, or processes.
+        <x:v>FINAL ANSWER GUARDRAILS:
+1. Use company facts and supported figures only.
+2. Remove source names, source pages, PDF references, citation language, and reviewer follow-up wording.
+3. Do not invent figures, targets, organizations, certifications, incidents, or processes.
+4. Keep source/page/RAG trace only in metadata columns, never in Final Answer.
+5. Avoid raw OCR fragments or report headers; Final Answer should read like polished ESG report text.
 Style Options: • formal: ESG report tone; cover short qualitative facts with owner and evidence; suitable when source evidence is complete.
 • concise: 1-2 compact sentences; use when the company has limited evidence or the item only needs a factual status.
 • evidence-led: start with reporting period/source/scope, then explain the policy, activity, or metric; best for reviewer traceability.
@@ -2380,14 +2505,17 @@
 • Never copy 동종산업 references as wording; they are only topic/scope references.</x:v>
       </x:c>
       <x:c r="R17" s="9" t="str">
-        <x:v>SUFFICIENT: write a complete report paragraph with scope, governance/process, activity, and KPI or limitation where relevant.
-PARTIAL: disclose supported facts only and phrase missing data as a disclosure limitation, not as an audit note.
+        <x:v>COVERAGE HANDLING:
+SUFFICIENT: write a complete ESG report paragraph with scope, governance/process, activity, and KPI or business limitation where relevant.
+PARTIAL: disclose supported facts only and phrase missing data as a business disclosure limitation, not as an audit note.
 NO DATA: state that the company has not disclosed or has not yet managed the item, without source tracing.</x:v>
       </x:c>
       <x:c r="S17" s="9" t="str">
-        <x:v>When quantitative support exists, include period, unit, boundary, and trend if available.
-When quantitative support is unavailable, do not convert blanks, dashes, or missing values to zero.
-Keep metrics inside the report prose, not as source evidence notes.</x:v>
+        <x:v>METRIC HANDLING:
+1. When quantitative support exists, include period, unit, boundary, and trend if available.
+2. When quantitative support is unavailable, do not convert blanks, dashes, or missing values to zero.
+3. Keep metrics inside the report prose, not as source evidence notes.
+4. Do not write the rule itself in Final Answer; apply it silently.</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -2460,10 +2588,12 @@
         <x:v>사회 / 거버넌스 (Governance) / 정보보호 관리 조직</x:v>
       </x:c>
       <x:c r="P18" s="9" t="str">
-        <x:v>Use ESG report-ready Korean prose.
-Cover the relevant content slots before adding optional context.
-Prefer 4-6 sentences when evidence is sufficient; keep partial rows factual and bounded.
-Do not include source/page/reviewer/audit-trace wording in Final Answer.
+        <x:v>ROW-LEVEL OUTPUT RULES:
+1. Use ESG report-ready Korean prose, not reviewer/audit instructions.
+2. Cover the relevant content slots before adding optional context.
+3. Prefer 4-6 substantive sentences when evidence is sufficient; keep partial rows factual and bounded.
+4. Do not include source/page/PDF/reviewer/audit-trace wording in Final Answer.
+5. Do not include template/meta instructions such as estimation rules, reviewer guidance, or final wording guidance.
 Content Slots: • Disclosure item: 정보보호 관리 조직
 • Required material 1: 전담 조직·위원회 구성
 • Required material 2: 역할과 책임(R&amp;R)
@@ -2475,9 +2605,12 @@
 • Do not convert these slots into a final sentence until company-specific facts are supplied.</x:v>
       </x:c>
       <x:c r="Q18" s="9" t="str">
-        <x:v>Final Answer may use company facts and supported figures only.
-Remove source names, source pages, PDF references, citation language, and reviewer follow-up wording.
-Do not invent figures, targets, organizations, certifications, incidents, or processes.
+        <x:v>FINAL ANSWER GUARDRAILS:
+1. Use company facts and supported figures only.
+2. Remove source names, source pages, PDF references, citation language, and reviewer follow-up wording.
+3. Do not invent figures, targets, organizations, certifications, incidents, or processes.
+4. Keep source/page/RAG trace only in metadata columns, never in Final Answer.
+5. Avoid raw OCR fragments or report headers; Final Answer should read like polished ESG report text.
 Style Options: • formal: ESG report tone; cover short qualitative facts with owner and evidence; suitable when source evidence is complete.
 • concise: 1-2 compact sentences; use when the company has limited evidence or the item only needs a factual status.
 • evidence-led: start with reporting period/source/scope, then explain the policy, activity, or metric; best for reviewer traceability.
@@ -2493,14 +2626,17 @@
 • Never copy 동종산업 references as wording; they are only topic/scope references.</x:v>
       </x:c>
       <x:c r="R18" s="9" t="str">
-        <x:v>SUFFICIENT: write a complete report paragraph with scope, governance/process, activity, and KPI or limitation where relevant.
-PARTIAL: disclose supported facts only and phrase missing data as a disclosure limitation, not as an audit note.
+        <x:v>COVERAGE HANDLING:
+SUFFICIENT: write a complete ESG report paragraph with scope, governance/process, activity, and KPI or business limitation where relevant.
+PARTIAL: disclose supported facts only and phrase missing data as a business disclosure limitation, not as an audit note.
 NO DATA: state that the company has not disclosed or has not yet managed the item, without source tracing.</x:v>
       </x:c>
       <x:c r="S18" s="9" t="str">
-        <x:v>When quantitative support exists, include period, unit, boundary, and trend if available.
-When quantitative support is unavailable, do not convert blanks, dashes, or missing values to zero.
-Keep metrics inside the report prose, not as source evidence notes.</x:v>
+        <x:v>METRIC HANDLING:
+1. When quantitative support exists, include period, unit, boundary, and trend if available.
+2. When quantitative support is unavailable, do not convert blanks, dashes, or missing values to zero.
+3. Keep metrics inside the report prose, not as source evidence notes.
+4. Do not write the rule itself in Final Answer; apply it silently.</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -2573,10 +2709,12 @@
         <x:v>사회 / 위험 관리 (Risk Management) / 정보보안 및 개인정보 보호 리스크 관리</x:v>
       </x:c>
       <x:c r="P19" s="9" t="str">
-        <x:v>Use ESG report-ready Korean prose.
-Cover the relevant content slots before adding optional context.
-Prefer 4-6 sentences when evidence is sufficient; keep partial rows factual and bounded.
-Do not include source/page/reviewer/audit-trace wording in Final Answer.
+        <x:v>ROW-LEVEL OUTPUT RULES:
+1. Use ESG report-ready Korean prose, not reviewer/audit instructions.
+2. Cover the relevant content slots before adding optional context.
+3. Prefer 4-6 substantive sentences when evidence is sufficient; keep partial rows factual and bounded.
+4. Do not include source/page/PDF/reviewer/audit-trace wording in Final Answer.
+5. Do not include template/meta instructions such as estimation rules, reviewer guidance, or final wording guidance.
 Content Slots: • Disclosure item: 정보보안 및 개인정보 보호 리스크 관리
 • Required material 1: 리스크 식별 절차
 • Required material 2: 평가·우선순위화
@@ -2588,9 +2726,12 @@
 • Do not convert these slots into a final sentence until company-specific facts are supplied.</x:v>
       </x:c>
       <x:c r="Q19" s="9" t="str">
-        <x:v>Final Answer may use company facts and supported figures only.
-Remove source names, source pages, PDF references, citation language, and reviewer follow-up wording.
-Do not invent figures, targets, organizations, certifications, incidents, or processes.
+        <x:v>FINAL ANSWER GUARDRAILS:
+1. Use company facts and supported figures only.
+2. Remove source names, source pages, PDF references, citation language, and reviewer follow-up wording.
+3. Do not invent figures, targets, organizations, certifications, incidents, or processes.
+4. Keep source/page/RAG trace only in metadata columns, never in Final Answer.
+5. Avoid raw OCR fragments or report headers; Final Answer should read like polished ESG report text.
 Style Options: • formal: ESG report tone; cover short qualitative facts with owner and evidence; suitable when source evidence is complete.
 • concise: 1-2 compact sentences; use when the company has limited evidence or the item only needs a factual status.
 • evidence-led: start with period, boundary, unit, and source system, then state value/status; if unavailable, state 미집계/해당사항 없음.
@@ -2606,14 +2747,17 @@
 • Never copy 동종산업 references as wording; they are only topic/scope references.</x:v>
       </x:c>
       <x:c r="R19" s="9" t="str">
-        <x:v>SUFFICIENT: write a complete report paragraph with scope, governance/process, activity, and KPI or limitation where relevant.
-PARTIAL: disclose supported facts only and phrase missing data as a disclosure limitation, not as an audit note.
+        <x:v>COVERAGE HANDLING:
+SUFFICIENT: write a complete ESG report paragraph with scope, governance/process, activity, and KPI or business limitation where relevant.
+PARTIAL: disclose supported facts only and phrase missing data as a business disclosure limitation, not as an audit note.
 NO DATA: state that the company has not disclosed or has not yet managed the item, without source tracing.</x:v>
       </x:c>
       <x:c r="S19" s="9" t="str">
-        <x:v>When quantitative support exists, include period, unit, boundary, and trend if available.
-When quantitative support is unavailable, do not convert blanks, dashes, or missing values to zero.
-Keep metrics inside the report prose, not as source evidence notes.</x:v>
+        <x:v>METRIC HANDLING:
+1. When quantitative support exists, include period, unit, boundary, and trend if available.
+2. When quantitative support is unavailable, do not convert blanks, dashes, or missing values to zero.
+3. Keep metrics inside the report prose, not as source evidence notes.
+4. Do not write the rule itself in Final Answer; apply it silently.</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -2689,10 +2833,12 @@
         <x:v>사회 / 지표 (Metrics) / 개인정보 침해 및 정보보안 사고 현황</x:v>
       </x:c>
       <x:c r="P20" s="9" t="str">
-        <x:v>Use ESG report-ready Korean prose.
-Cover the relevant content slots before adding optional context.
-Prefer 4-6 sentences when evidence is sufficient; keep partial rows factual and bounded.
-Do not include source/page/reviewer/audit-trace wording in Final Answer.
+        <x:v>ROW-LEVEL OUTPUT RULES:
+1. Use ESG report-ready Korean prose, not reviewer/audit instructions.
+2. Cover the relevant content slots before adding optional context.
+3. Prefer 4-6 substantive sentences when evidence is sufficient; keep partial rows factual and bounded.
+4. Do not include source/page/PDF/reviewer/audit-trace wording in Final Answer.
+5. Do not include template/meta instructions such as estimation rules, reviewer guidance, or final wording guidance.
 Content Slots: • Disclosure item: 개인정보 침해 및 정보보안 사고 현황
 • Required material 1: 핵심 성과지표(KPI) 정의
 • Required material 2: 최근 실적 수치
@@ -2705,9 +2851,12 @@
 • Do not convert these slots into a final sentence until company-specific facts are supplied.</x:v>
       </x:c>
       <x:c r="Q20" s="9" t="str">
-        <x:v>Final Answer may use company facts and supported figures only.
-Remove source names, source pages, PDF references, citation language, and reviewer follow-up wording.
-Do not invent figures, targets, organizations, certifications, incidents, or processes.
+        <x:v>FINAL ANSWER GUARDRAILS:
+1. Use company facts and supported figures only.
+2. Remove source names, source pages, PDF references, citation language, and reviewer follow-up wording.
+3. Do not invent figures, targets, organizations, certifications, incidents, or processes.
+4. Keep source/page/RAG trace only in metadata columns, never in Final Answer.
+5. Avoid raw OCR fragments or report headers; Final Answer should read like polished ESG report text.
 Style Options: • formal: ESG report tone; cover short qualitative facts with owner and evidence; suitable when source evidence is complete.
 • concise: 1-2 compact sentences; use when the company has limited evidence or the item only needs a factual status.
 • evidence-led: start with period, boundary, unit, and source system, then state value/status; if unavailable, state 미집계/해당사항 없음.
@@ -2723,14 +2872,17 @@
 • Never copy 동종산업 references as wording; they are only topic/scope references.</x:v>
       </x:c>
       <x:c r="R20" s="9" t="str">
-        <x:v>SUFFICIENT: write a complete report paragraph with scope, governance/process, activity, and KPI or limitation where relevant.
-PARTIAL: disclose supported facts only and phrase missing data as a disclosure limitation, not as an audit note.
+        <x:v>COVERAGE HANDLING:
+SUFFICIENT: write a complete ESG report paragraph with scope, governance/process, activity, and KPI or business limitation where relevant.
+PARTIAL: disclose supported facts only and phrase missing data as a business disclosure limitation, not as an audit note.
 NO DATA: state that the company has not disclosed or has not yet managed the item, without source tracing.</x:v>
       </x:c>
       <x:c r="S20" s="9" t="str">
-        <x:v>When quantitative support exists, include period, unit, boundary, and trend if available.
-When quantitative support is unavailable, do not convert blanks, dashes, or missing values to zero.
-Keep metrics inside the report prose, not as source evidence notes.</x:v>
+        <x:v>METRIC HANDLING:
+1. When quantitative support exists, include period, unit, boundary, and trend if available.
+2. When quantitative support is unavailable, do not convert blanks, dashes, or missing values to zero.
+3. Keep metrics inside the report prose, not as source evidence notes.
+4. Do not write the rule itself in Final Answer; apply it silently.</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -2803,10 +2955,12 @@
         <x:v>환경 / 전략 (Strategy) / 환경경영 정책 및 목표</x:v>
       </x:c>
       <x:c r="P21" s="9" t="str">
-        <x:v>Use ESG report-ready Korean prose.
-Cover the relevant content slots before adding optional context.
-Prefer 4-6 sentences when evidence is sufficient; keep partial rows factual and bounded.
-Do not include source/page/reviewer/audit-trace wording in Final Answer.
+        <x:v>ROW-LEVEL OUTPUT RULES:
+1. Use ESG report-ready Korean prose, not reviewer/audit instructions.
+2. Cover the relevant content slots before adding optional context.
+3. Prefer 4-6 substantive sentences when evidence is sufficient; keep partial rows factual and bounded.
+4. Do not include source/page/PDF/reviewer/audit-trace wording in Final Answer.
+5. Do not include template/meta instructions such as estimation rules, reviewer guidance, or final wording guidance.
 Content Slots: • Disclosure item: 환경경영 정책 및 목표
 • Required material 1: 추진 배경·중요성
 • Required material 2: 정책·방침 선언
@@ -2818,9 +2972,12 @@
 • Do not convert these slots into a final sentence until company-specific facts are supplied.</x:v>
       </x:c>
       <x:c r="Q21" s="9" t="str">
-        <x:v>Final Answer may use company facts and supported figures only.
-Remove source names, source pages, PDF references, citation language, and reviewer follow-up wording.
-Do not invent figures, targets, organizations, certifications, incidents, or processes.
+        <x:v>FINAL ANSWER GUARDRAILS:
+1. Use company facts and supported figures only.
+2. Remove source names, source pages, PDF references, citation language, and reviewer follow-up wording.
+3. Do not invent figures, targets, organizations, certifications, incidents, or processes.
+4. Keep source/page/RAG trace only in metadata columns, never in Final Answer.
+5. Avoid raw OCR fragments or report headers; Final Answer should read like polished ESG report text.
 Style Options: • formal: ESG report tone; cover short qualitative facts with owner and evidence; suitable when source evidence is complete.
 • concise: 1-2 compact sentences; use when the company has limited evidence or the item only needs a factual status.
 • evidence-led: start with reporting period/source/scope, then explain the policy, activity, or metric; best for reviewer traceability.
@@ -2836,14 +2993,17 @@
 • Never copy 동종산업 references as wording; they are only topic/scope references.</x:v>
       </x:c>
       <x:c r="R21" s="9" t="str">
-        <x:v>SUFFICIENT: write a complete report paragraph with scope, governance/process, activity, and KPI or limitation where relevant.
-PARTIAL: disclose supported facts only and phrase missing data as a disclosure limitation, not as an audit note.
+        <x:v>COVERAGE HANDLING:
+SUFFICIENT: write a complete ESG report paragraph with scope, governance/process, activity, and KPI or business limitation where relevant.
+PARTIAL: disclose supported facts only and phrase missing data as a business disclosure limitation, not as an audit note.
 NO DATA: state that the company has not disclosed or has not yet managed the item, without source tracing.</x:v>
       </x:c>
       <x:c r="S21" s="9" t="str">
-        <x:v>When quantitative support exists, include period, unit, boundary, and trend if available.
-When quantitative support is unavailable, do not convert blanks, dashes, or missing values to zero.
-Keep metrics inside the report prose, not as source evidence notes.</x:v>
+        <x:v>METRIC HANDLING:
+1. When quantitative support exists, include period, unit, boundary, and trend if available.
+2. When quantitative support is unavailable, do not convert blanks, dashes, or missing values to zero.
+3. Keep metrics inside the report prose, not as source evidence notes.
+4. Do not write the rule itself in Final Answer; apply it silently.</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -2916,10 +3076,12 @@
         <x:v>환경 / 거버넌스 (Governance) / 환경경영 조직 및 책임</x:v>
       </x:c>
       <x:c r="P22" s="9" t="str">
-        <x:v>Use ESG report-ready Korean prose.
-Cover the relevant content slots before adding optional context.
-Prefer 4-6 sentences when evidence is sufficient; keep partial rows factual and bounded.
-Do not include source/page/reviewer/audit-trace wording in Final Answer.
+        <x:v>ROW-LEVEL OUTPUT RULES:
+1. Use ESG report-ready Korean prose, not reviewer/audit instructions.
+2. Cover the relevant content slots before adding optional context.
+3. Prefer 4-6 substantive sentences when evidence is sufficient; keep partial rows factual and bounded.
+4. Do not include source/page/PDF/reviewer/audit-trace wording in Final Answer.
+5. Do not include template/meta instructions such as estimation rules, reviewer guidance, or final wording guidance.
 Content Slots: • Disclosure item: 환경경영 조직 및 책임
 • Required material 1: 전담 조직·위원회 구성
 • Required material 2: 역할과 책임(R&amp;R)
@@ -2931,9 +3093,12 @@
 • Do not convert these slots into a final sentence until company-specific facts are supplied.</x:v>
       </x:c>
       <x:c r="Q22" s="9" t="str">
-        <x:v>Final Answer may use company facts and supported figures only.
-Remove source names, source pages, PDF references, citation language, and reviewer follow-up wording.
-Do not invent figures, targets, organizations, certifications, incidents, or processes.
+        <x:v>FINAL ANSWER GUARDRAILS:
+1. Use company facts and supported figures only.
+2. Remove source names, source pages, PDF references, citation language, and reviewer follow-up wording.
+3. Do not invent figures, targets, organizations, certifications, incidents, or processes.
+4. Keep source/page/RAG trace only in metadata columns, never in Final Answer.
+5. Avoid raw OCR fragments or report headers; Final Answer should read like polished ESG report text.
 Style Options: • formal: ESG report tone; cover short qualitative facts with owner and evidence; suitable when source evidence is complete.
 • concise: 1-2 compact sentences; use when the company has limited evidence or the item only needs a factual status.
 • evidence-led: start with reporting period/source/scope, then explain the policy, activity, or metric; best for reviewer traceability.
@@ -2949,14 +3114,17 @@
 • Never copy 동종산업 references as wording; they are only topic/scope references.</x:v>
       </x:c>
       <x:c r="R22" s="9" t="str">
-        <x:v>SUFFICIENT: write a complete report paragraph with scope, governance/process, activity, and KPI or limitation where relevant.
-PARTIAL: disclose supported facts only and phrase missing data as a disclosure limitation, not as an audit note.
+        <x:v>COVERAGE HANDLING:
+SUFFICIENT: write a complete ESG report paragraph with scope, governance/process, activity, and KPI or business limitation where relevant.
+PARTIAL: disclose supported facts only and phrase missing data as a business disclosure limitation, not as an audit note.
 NO DATA: state that the company has not disclosed or has not yet managed the item, without source tracing.</x:v>
       </x:c>
       <x:c r="S22" s="9" t="str">
-        <x:v>When quantitative support exists, include period, unit, boundary, and trend if available.
-When quantitative support is unavailable, do not convert blanks, dashes, or missing values to zero.
-Keep metrics inside the report prose, not as source evidence notes.</x:v>
+        <x:v>METRIC HANDLING:
+1. When quantitative support exists, include period, unit, boundary, and trend if available.
+2. When quantitative support is unavailable, do not convert blanks, dashes, or missing values to zero.
+3. Keep metrics inside the report prose, not as source evidence notes.
+4. Do not write the rule itself in Final Answer; apply it silently.</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -3029,10 +3197,12 @@
         <x:v>환경 / 위험 관리 (Risk Management) / 환경 영향 및 환경 리스크 관리</x:v>
       </x:c>
       <x:c r="P23" s="9" t="str">
-        <x:v>Use ESG report-ready Korean prose.
-Cover the relevant content slots before adding optional context.
-Prefer 4-6 sentences when evidence is sufficient; keep partial rows factual and bounded.
-Do not include source/page/reviewer/audit-trace wording in Final Answer.
+        <x:v>ROW-LEVEL OUTPUT RULES:
+1. Use ESG report-ready Korean prose, not reviewer/audit instructions.
+2. Cover the relevant content slots before adding optional context.
+3. Prefer 4-6 substantive sentences when evidence is sufficient; keep partial rows factual and bounded.
+4. Do not include source/page/PDF/reviewer/audit-trace wording in Final Answer.
+5. Do not include template/meta instructions such as estimation rules, reviewer guidance, or final wording guidance.
 Content Slots: • Disclosure item: 환경 영향 및 환경 리스크 관리
 • Required material 1: 리스크 식별 절차
 • Required material 2: 평가·우선순위화
@@ -3044,9 +3214,12 @@
 • Do not convert these slots into a final sentence until company-specific facts are supplied.</x:v>
       </x:c>
       <x:c r="Q23" s="9" t="str">
-        <x:v>Final Answer may use company facts and supported figures only.
-Remove source names, source pages, PDF references, citation language, and reviewer follow-up wording.
-Do not invent figures, targets, organizations, certifications, incidents, or processes.
+        <x:v>FINAL ANSWER GUARDRAILS:
+1. Use company facts and supported figures only.
+2. Remove source names, source pages, PDF references, citation language, and reviewer follow-up wording.
+3. Do not invent figures, targets, organizations, certifications, incidents, or processes.
+4. Keep source/page/RAG trace only in metadata columns, never in Final Answer.
+5. Avoid raw OCR fragments or report headers; Final Answer should read like polished ESG report text.
 Style Options: • formal: ESG report tone; cover short qualitative facts with owner and evidence; suitable when source evidence is complete.
 • concise: 1-2 compact sentences; use when the company has limited evidence or the item only needs a factual status.
 • evidence-led: start with reporting period/source/scope, then explain the policy, activity, or metric; best for reviewer traceability.
@@ -3062,14 +3235,17 @@
 • Never copy 동종산업 references as wording; they are only topic/scope references.</x:v>
       </x:c>
       <x:c r="R23" s="9" t="str">
-        <x:v>SUFFICIENT: write a complete report paragraph with scope, governance/process, activity, and KPI or limitation where relevant.
-PARTIAL: disclose supported facts only and phrase missing data as a disclosure limitation, not as an audit note.
+        <x:v>COVERAGE HANDLING:
+SUFFICIENT: write a complete ESG report paragraph with scope, governance/process, activity, and KPI or business limitation where relevant.
+PARTIAL: disclose supported facts only and phrase missing data as a business disclosure limitation, not as an audit note.
 NO DATA: state that the company has not disclosed or has not yet managed the item, without source tracing.</x:v>
       </x:c>
       <x:c r="S23" s="9" t="str">
-        <x:v>When quantitative support exists, include period, unit, boundary, and trend if available.
-When quantitative support is unavailable, do not convert blanks, dashes, or missing values to zero.
-Keep metrics inside the report prose, not as source evidence notes.</x:v>
+        <x:v>METRIC HANDLING:
+1. When quantitative support exists, include period, unit, boundary, and trend if available.
+2. When quantitative support is unavailable, do not convert blanks, dashes, or missing values to zero.
+3. Keep metrics inside the report prose, not as source evidence notes.
+4. Do not write the rule itself in Final Answer; apply it silently.</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -3145,10 +3321,12 @@
         <x:v>환경 / 지표 (Metrics) / 환경 성과 지표 및 환경 사고 현황</x:v>
       </x:c>
       <x:c r="P24" s="9" t="str">
-        <x:v>Use ESG report-ready Korean prose.
-Cover the relevant content slots before adding optional context.
-Prefer 4-6 sentences when evidence is sufficient; keep partial rows factual and bounded.
-Do not include source/page/reviewer/audit-trace wording in Final Answer.
+        <x:v>ROW-LEVEL OUTPUT RULES:
+1. Use ESG report-ready Korean prose, not reviewer/audit instructions.
+2. Cover the relevant content slots before adding optional context.
+3. Prefer 4-6 substantive sentences when evidence is sufficient; keep partial rows factual and bounded.
+4. Do not include source/page/PDF/reviewer/audit-trace wording in Final Answer.
+5. Do not include template/meta instructions such as estimation rules, reviewer guidance, or final wording guidance.
 Content Slots: • Disclosure item: 환경 성과 지표 및 환경 사고 현황
 • Required material 1: 핵심 성과지표(KPI) 정의
 • Required material 2: 최근 실적 수치
@@ -3161,9 +3339,12 @@
 • Do not convert these slots into a final sentence until company-specific facts are supplied.</x:v>
       </x:c>
       <x:c r="Q24" s="9" t="str">
-        <x:v>Final Answer may use company facts and supported figures only.
-Remove source names, source pages, PDF references, citation language, and reviewer follow-up wording.
-Do not invent figures, targets, organizations, certifications, incidents, or processes.
+        <x:v>FINAL ANSWER GUARDRAILS:
+1. Use company facts and supported figures only.
+2. Remove source names, source pages, PDF references, citation language, and reviewer follow-up wording.
+3. Do not invent figures, targets, organizations, certifications, incidents, or processes.
+4. Keep source/page/RAG trace only in metadata columns, never in Final Answer.
+5. Avoid raw OCR fragments or report headers; Final Answer should read like polished ESG report text.
 Style Options: • formal: ESG report tone; cover short qualitative facts with owner and evidence; suitable when source evidence is complete.
 • concise: 1-2 compact sentences; use when the company has limited evidence or the item only needs a factual status.
 • evidence-led: start with period, boundary, unit, and source system, then state value/status; if unavailable, state 미집계/해당사항 없음.
@@ -3179,14 +3360,17 @@
 • Never copy 동종산업 references as wording; they are only topic/scope references.</x:v>
       </x:c>
       <x:c r="R24" s="9" t="str">
-        <x:v>SUFFICIENT: write a complete report paragraph with scope, governance/process, activity, and KPI or limitation where relevant.
-PARTIAL: disclose supported facts only and phrase missing data as a disclosure limitation, not as an audit note.
+        <x:v>COVERAGE HANDLING:
+SUFFICIENT: write a complete ESG report paragraph with scope, governance/process, activity, and KPI or business limitation where relevant.
+PARTIAL: disclose supported facts only and phrase missing data as a business disclosure limitation, not as an audit note.
 NO DATA: state that the company has not disclosed or has not yet managed the item, without source tracing.</x:v>
       </x:c>
       <x:c r="S24" s="9" t="str">
-        <x:v>When quantitative support exists, include period, unit, boundary, and trend if available.
-When quantitative support is unavailable, do not convert blanks, dashes, or missing values to zero.
-Keep metrics inside the report prose, not as source evidence notes.</x:v>
+        <x:v>METRIC HANDLING:
+1. When quantitative support exists, include period, unit, boundary, and trend if available.
+2. When quantitative support is unavailable, do not convert blanks, dashes, or missing values to zero.
+3. Keep metrics inside the report prose, not as source evidence notes.
+4. Do not write the rule itself in Final Answer; apply it silently.</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -3259,10 +3443,12 @@
         <x:v>거버넌스 / 전략 (Strategy) / 윤리경영 정책 및 목표</x:v>
       </x:c>
       <x:c r="P25" s="9" t="str">
-        <x:v>Use ESG report-ready Korean prose.
-Cover the relevant content slots before adding optional context.
-Prefer 4-6 sentences when evidence is sufficient; keep partial rows factual and bounded.
-Do not include source/page/reviewer/audit-trace wording in Final Answer.
+        <x:v>ROW-LEVEL OUTPUT RULES:
+1. Use ESG report-ready Korean prose, not reviewer/audit instructions.
+2. Cover the relevant content slots before adding optional context.
+3. Prefer 4-6 substantive sentences when evidence is sufficient; keep partial rows factual and bounded.
+4. Do not include source/page/PDF/reviewer/audit-trace wording in Final Answer.
+5. Do not include template/meta instructions such as estimation rules, reviewer guidance, or final wording guidance.
 Content Slots: • Disclosure item: 윤리경영 정책 및 목표
 • Required material 1: 추진 배경·중요성
 • Required material 2: 정책·방침 선언
@@ -3274,9 +3460,12 @@
 • Do not convert these slots into a final sentence until company-specific facts are supplied.</x:v>
       </x:c>
       <x:c r="Q25" s="9" t="str">
-        <x:v>Final Answer may use company facts and supported figures only.
-Remove source names, source pages, PDF references, citation language, and reviewer follow-up wording.
-Do not invent figures, targets, organizations, certifications, incidents, or processes.
+        <x:v>FINAL ANSWER GUARDRAILS:
+1. Use company facts and supported figures only.
+2. Remove source names, source pages, PDF references, citation language, and reviewer follow-up wording.
+3. Do not invent figures, targets, organizations, certifications, incidents, or processes.
+4. Keep source/page/RAG trace only in metadata columns, never in Final Answer.
+5. Avoid raw OCR fragments or report headers; Final Answer should read like polished ESG report text.
 Style Options: • formal: ESG report tone; cover short qualitative facts with owner and evidence; suitable when source evidence is complete.
 • concise: 1-2 compact sentences; use when the company has limited evidence or the item only needs a factual status.
 • evidence-led: start with reporting period/source/scope, then explain the policy, activity, or metric; best for reviewer traceability.
@@ -3292,14 +3481,17 @@
 • Never copy 동종산업 references as wording; they are only topic/scope references.</x:v>
       </x:c>
       <x:c r="R25" s="9" t="str">
-        <x:v>SUFFICIENT: write a complete report paragraph with scope, governance/process, activity, and KPI or limitation where relevant.
-PARTIAL: disclose supported facts only and phrase missing data as a disclosure limitation, not as an audit note.
+        <x:v>COVERAGE HANDLING:
+SUFFICIENT: write a complete ESG report paragraph with scope, governance/process, activity, and KPI or business limitation where relevant.
+PARTIAL: disclose supported facts only and phrase missing data as a business disclosure limitation, not as an audit note.
 NO DATA: state that the company has not disclosed or has not yet managed the item, without source tracing.</x:v>
       </x:c>
       <x:c r="S25" s="9" t="str">
-        <x:v>When quantitative support exists, include period, unit, boundary, and trend if available.
-When quantitative support is unavailable, do not convert blanks, dashes, or missing values to zero.
-Keep metrics inside the report prose, not as source evidence notes.</x:v>
+        <x:v>METRIC HANDLING:
+1. When quantitative support exists, include period, unit, boundary, and trend if available.
+2. When quantitative support is unavailable, do not convert blanks, dashes, or missing values to zero.
+3. Keep metrics inside the report prose, not as source evidence notes.
+4. Do not write the rule itself in Final Answer; apply it silently.</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -3372,10 +3564,12 @@
         <x:v>거버넌스 / 거버넌스 (Governance) / 윤리경영 조직 및 운영 체계</x:v>
       </x:c>
       <x:c r="P26" s="9" t="str">
-        <x:v>Use ESG report-ready Korean prose.
-Cover the relevant content slots before adding optional context.
-Prefer 4-6 sentences when evidence is sufficient; keep partial rows factual and bounded.
-Do not include source/page/reviewer/audit-trace wording in Final Answer.
+        <x:v>ROW-LEVEL OUTPUT RULES:
+1. Use ESG report-ready Korean prose, not reviewer/audit instructions.
+2. Cover the relevant content slots before adding optional context.
+3. Prefer 4-6 substantive sentences when evidence is sufficient; keep partial rows factual and bounded.
+4. Do not include source/page/PDF/reviewer/audit-trace wording in Final Answer.
+5. Do not include template/meta instructions such as estimation rules, reviewer guidance, or final wording guidance.
 Content Slots: • Disclosure item: 윤리경영 조직 및 운영 체계
 • Required material 1: 전담 조직·위원회 구성
 • Required material 2: 역할과 책임(R&amp;R)
@@ -3387,9 +3581,12 @@
 • Do not convert these slots into a final sentence until company-specific facts are supplied.</x:v>
       </x:c>
       <x:c r="Q26" s="9" t="str">
-        <x:v>Final Answer may use company facts and supported figures only.
-Remove source names, source pages, PDF references, citation language, and reviewer follow-up wording.
-Do not invent figures, targets, organizations, certifications, incidents, or processes.
+        <x:v>FINAL ANSWER GUARDRAILS:
+1. Use company facts and supported figures only.
+2. Remove source names, source pages, PDF references, citation language, and reviewer follow-up wording.
+3. Do not invent figures, targets, organizations, certifications, incidents, or processes.
+4. Keep source/page/RAG trace only in metadata columns, never in Final Answer.
+5. Avoid raw OCR fragments or report headers; Final Answer should read like polished ESG report text.
 Style Options: • formal: ESG report tone; cover short qualitative facts with owner and evidence; suitable when source evidence is complete.
 • concise: 1-2 compact sentences; use when the company has limited evidence or the item only needs a factual status.
 • evidence-led: start with reporting period/source/scope, then explain the policy, activity, or metric; best for reviewer traceability.
@@ -3405,14 +3602,17 @@
 • Never copy 동종산업 references as wording; they are only topic/scope references.</x:v>
       </x:c>
       <x:c r="R26" s="9" t="str">
-        <x:v>SUFFICIENT: write a complete report paragraph with scope, governance/process, activity, and KPI or limitation where relevant.
-PARTIAL: disclose supported facts only and phrase missing data as a disclosure limitation, not as an audit note.
+        <x:v>COVERAGE HANDLING:
+SUFFICIENT: write a complete ESG report paragraph with scope, governance/process, activity, and KPI or business limitation where relevant.
+PARTIAL: disclose supported facts only and phrase missing data as a business disclosure limitation, not as an audit note.
 NO DATA: state that the company has not disclosed or has not yet managed the item, without source tracing.</x:v>
       </x:c>
       <x:c r="S26" s="9" t="str">
-        <x:v>When quantitative support exists, include period, unit, boundary, and trend if available.
-When quantitative support is unavailable, do not convert blanks, dashes, or missing values to zero.
-Keep metrics inside the report prose, not as source evidence notes.</x:v>
+        <x:v>METRIC HANDLING:
+1. When quantitative support exists, include period, unit, boundary, and trend if available.
+2. When quantitative support is unavailable, do not convert blanks, dashes, or missing values to zero.
+3. Keep metrics inside the report prose, not as source evidence notes.
+4. Do not write the rule itself in Final Answer; apply it silently.</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -3485,10 +3685,12 @@
         <x:v>거버넌스 / 위험 관리 (Risk Management) / 윤리 및 준법 리스크 관리</x:v>
       </x:c>
       <x:c r="P27" s="9" t="str">
-        <x:v>Use ESG report-ready Korean prose.
-Cover the relevant content slots before adding optional context.
-Prefer 4-6 sentences when evidence is sufficient; keep partial rows factual and bounded.
-Do not include source/page/reviewer/audit-trace wording in Final Answer.
+        <x:v>ROW-LEVEL OUTPUT RULES:
+1. Use ESG report-ready Korean prose, not reviewer/audit instructions.
+2. Cover the relevant content slots before adding optional context.
+3. Prefer 4-6 substantive sentences when evidence is sufficient; keep partial rows factual and bounded.
+4. Do not include source/page/PDF/reviewer/audit-trace wording in Final Answer.
+5. Do not include template/meta instructions such as estimation rules, reviewer guidance, or final wording guidance.
 Content Slots: • Disclosure item: 윤리 및 준법 리스크 관리
 • Required material 1: 리스크 식별 절차
 • Required material 2: 평가·우선순위화
@@ -3500,9 +3702,12 @@
 • Do not convert these slots into a final sentence until company-specific facts are supplied.</x:v>
       </x:c>
       <x:c r="Q27" s="9" t="str">
-        <x:v>Final Answer may use company facts and supported figures only.
-Remove source names, source pages, PDF references, citation language, and reviewer follow-up wording.
-Do not invent figures, targets, organizations, certifications, incidents, or processes.
+        <x:v>FINAL ANSWER GUARDRAILS:
+1. Use company facts and supported figures only.
+2. Remove source names, source pages, PDF references, citation language, and reviewer follow-up wording.
+3. Do not invent figures, targets, organizations, certifications, incidents, or processes.
+4. Keep source/page/RAG trace only in metadata columns, never in Final Answer.
+5. Avoid raw OCR fragments or report headers; Final Answer should read like polished ESG report text.
 Style Options: • formal: ESG report tone; cover short qualitative facts with owner and evidence; suitable when source evidence is complete.
 • concise: 1-2 compact sentences; use when the company has limited evidence or the item only needs a factual status.
 • evidence-led: start with reporting period/source/scope, then explain the policy, activity, or metric; best for reviewer traceability.
@@ -3518,14 +3723,17 @@
 • Never copy 동종산업 references as wording; they are only topic/scope references.</x:v>
       </x:c>
       <x:c r="R27" s="9" t="str">
-        <x:v>SUFFICIENT: write a complete report paragraph with scope, governance/process, activity, and KPI or limitation where relevant.
-PARTIAL: disclose supported facts only and phrase missing data as a disclosure limitation, not as an audit note.
+        <x:v>COVERAGE HANDLING:
+SUFFICIENT: write a complete ESG report paragraph with scope, governance/process, activity, and KPI or business limitation where relevant.
+PARTIAL: disclose supported facts only and phrase missing data as a business disclosure limitation, not as an audit note.
 NO DATA: state that the company has not disclosed or has not yet managed the item, without source tracing.</x:v>
       </x:c>
       <x:c r="S27" s="9" t="str">
-        <x:v>When quantitative support exists, include period, unit, boundary, and trend if available.
-When quantitative support is unavailable, do not convert blanks, dashes, or missing values to zero.
-Keep metrics inside the report prose, not as source evidence notes.</x:v>
+        <x:v>METRIC HANDLING:
+1. When quantitative support exists, include period, unit, boundary, and trend if available.
+2. When quantitative support is unavailable, do not convert blanks, dashes, or missing values to zero.
+3. Keep metrics inside the report prose, not as source evidence notes.
+4. Do not write the rule itself in Final Answer; apply it silently.</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -3601,10 +3809,12 @@
         <x:v>거버넌스 / 지표 (Metrics) / 윤리 위반 및 준법 관련 사건 현황</x:v>
       </x:c>
       <x:c r="P28" s="9" t="str">
-        <x:v>Use ESG report-ready Korean prose.
-Cover the relevant content slots before adding optional context.
-Prefer 4-6 sentences when evidence is sufficient; keep partial rows factual and bounded.
-Do not include source/page/reviewer/audit-trace wording in Final Answer.
+        <x:v>ROW-LEVEL OUTPUT RULES:
+1. Use ESG report-ready Korean prose, not reviewer/audit instructions.
+2. Cover the relevant content slots before adding optional context.
+3. Prefer 4-6 substantive sentences when evidence is sufficient; keep partial rows factual and bounded.
+4. Do not include source/page/PDF/reviewer/audit-trace wording in Final Answer.
+5. Do not include template/meta instructions such as estimation rules, reviewer guidance, or final wording guidance.
 Content Slots: • Disclosure item: 윤리 위반 및 준법 관련 사건 현황
 • Required material 1: 핵심 성과지표(KPI) 정의
 • Required material 2: 최근 실적 수치
@@ -3617,9 +3827,12 @@
 • Do not convert these slots into a final sentence until company-specific facts are supplied.</x:v>
       </x:c>
       <x:c r="Q28" s="9" t="str">
-        <x:v>Final Answer may use company facts and supported figures only.
-Remove source names, source pages, PDF references, citation language, and reviewer follow-up wording.
-Do not invent figures, targets, organizations, certifications, incidents, or processes.
+        <x:v>FINAL ANSWER GUARDRAILS:
+1. Use company facts and supported figures only.
+2. Remove source names, source pages, PDF references, citation language, and reviewer follow-up wording.
+3. Do not invent figures, targets, organizations, certifications, incidents, or processes.
+4. Keep source/page/RAG trace only in metadata columns, never in Final Answer.
+5. Avoid raw OCR fragments or report headers; Final Answer should read like polished ESG report text.
 Style Options: • formal: ESG report tone; cover short qualitative facts with owner and evidence; suitable when source evidence is complete.
 • concise: 1-2 compact sentences; use when the company has limited evidence or the item only needs a factual status.
 • evidence-led: start with period, boundary, unit, and source system, then state value/status; if unavailable, state 미집계/해당사항 없음.
@@ -3635,14 +3848,17 @@
 • Never copy 동종산업 references as wording; they are only topic/scope references.</x:v>
       </x:c>
       <x:c r="R28" s="9" t="str">
-        <x:v>SUFFICIENT: write a complete report paragraph with scope, governance/process, activity, and KPI or limitation where relevant.
-PARTIAL: disclose supported facts only and phrase missing data as a disclosure limitation, not as an audit note.
+        <x:v>COVERAGE HANDLING:
+SUFFICIENT: write a complete ESG report paragraph with scope, governance/process, activity, and KPI or business limitation where relevant.
+PARTIAL: disclose supported facts only and phrase missing data as a business disclosure limitation, not as an audit note.
 NO DATA: state that the company has not disclosed or has not yet managed the item, without source tracing.</x:v>
       </x:c>
       <x:c r="S28" s="9" t="str">
-        <x:v>When quantitative support exists, include period, unit, boundary, and trend if available.
-When quantitative support is unavailable, do not convert blanks, dashes, or missing values to zero.
-Keep metrics inside the report prose, not as source evidence notes.</x:v>
+        <x:v>METRIC HANDLING:
+1. When quantitative support exists, include period, unit, boundary, and trend if available.
+2. When quantitative support is unavailable, do not convert blanks, dashes, or missing values to zero.
+3. Keep metrics inside the report prose, not as source evidence notes.
+4. Do not write the rule itself in Final Answer; apply it silently.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
